--- a/tools/import-cli/templates/CONTOH_TERISI.xlsx
+++ b/tools/import-cli/templates/CONTOH_TERISI.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="81">
   <si>
     <t>nama_kategori</t>
   </si>
@@ -156,6 +156,18 @@
     <t>stok_minimum</t>
   </si>
   <si>
+    <t>satuan_besar</t>
+  </si>
+  <si>
+    <t>isi</t>
+  </si>
+  <si>
+    <t>harga_satuan_besar</t>
+  </si>
+  <si>
+    <t>barcode_satuan_besar</t>
+  </si>
+  <si>
     <t>Tepung Terigu Segitiga Biru 1kg</t>
   </si>
   <si>
@@ -171,6 +183,9 @@
     <t>Segitiga Biru</t>
   </si>
   <si>
+    <t>Bal</t>
+  </si>
+  <si>
     <t>Gula Pasir 1kg</t>
   </si>
   <si>
@@ -190,6 +205,9 @@
   </si>
   <si>
     <t>Fermipan</t>
+  </si>
+  <si>
+    <t>Dus</t>
   </si>
   <si>
     <t>kode_produk_induk</t>
@@ -1016,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N201"/>
+  <dimension ref="A1:R201"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1030,9 +1048,13 @@
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="8" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -1075,13 +1097,25 @@
       <c r="N1" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -1096,16 +1130,16 @@
         <v>14000</v>
       </c>
       <c r="G2" s="3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>33</v>
@@ -1119,13 +1153,25 @@
       <c r="N2" s="3">
         <v>10</v>
       </c>
+      <c r="O2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="3">
+        <v>12</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>160000</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>3</v>
@@ -1143,13 +1189,13 @@
         <v>40</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>33</v>
@@ -1163,13 +1209,25 @@
       <c r="N3" s="3">
         <v>10</v>
       </c>
+      <c r="O3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>6</v>
@@ -1187,13 +1245,13 @@
         <v>100</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>33</v>
@@ -1206,6 +1264,18 @@
       </c>
       <c r="N4" s="3">
         <v>20</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="P4" s="3">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>110000</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="3:13" x14ac:dyDescent="0.25"/>
@@ -1450,13 +1520,13 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>37</v>
@@ -1471,16 +1541,16 @@
         <v>41</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25"/>
@@ -1728,24 +1798,24 @@
         <v>10</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D2" s="3">
         <v>12500</v>
@@ -1756,13 +1826,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D3" s="3">
         <v>13200</v>
@@ -2002,10 +2072,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>15</v>
@@ -2019,16 +2089,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>20</v>
